--- a/assets/docs/lop4/Dao duc - Lop 4.xlsx
+++ b/assets/docs/lop4/Dao duc - Lop 4.xlsx
@@ -827,7 +827,7 @@
         <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Yêu lao động”, GV chiếu bộ ảnh người lao động ở nhiều nghề và ảnh HS làm việc vừa sức như trực nhật, tưới cây, gấp quần áo
 Năng lực số Miền 2 (Cơ bản, bậc 2): GV gõ lên màn hình những việc HS kể thành bảng hai cột việc ở nhà và việc ở trường; cả lớp cùng đọc
-KNS: KN chi tiêu và giữ gìn: dùng đồ dùng, tiền bạc hợp lí, giữ gìn của công.</t>
+Học tập và làm theo Bác: Điều 2 “Học tập tốt, lao động tốt” (mạch 2): khi kể tấm gương yêu lao động, HS nêu điều mình học được và tự nhận một việc lao động vừa sức, làm đều đặn trong tuần ở nhà hoặc ở lớp.</t>
         </is>
       </c>
     </row>
